--- a/upload/execucao2022.xlsx
+++ b/upload/execucao2022.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,107 +421,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>NUMERO_SIAFI</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Número Empenho</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Data Registro Doc Empenho</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Número Processo Compra SIAD</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Unidade Orçamentária - Código</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Unidade Orçamentária - Sigla</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unidade Orçamentária - Nome</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Razão Social Credor</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CNPJ_CPF Credor - Formatado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Elemento Despesa - Código</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Elemento Despesa - Descrição</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Item Despesa - Código</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Item Despesa - Descrição</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Fonte Recurso - Código</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Fonte Recurso - Descrição</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Valor Despesa Empenhada</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Valor Despesa Liquidada</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Valor Despesa Liquidada</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Valor Pago Financeiro</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Valor Liquidado em RP</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Valor pago em RP</t>
         </is>
@@ -546,7 +534,7 @@
       <c r="B2" t="n">
         <v>362</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>44560</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -621,7 +609,7 @@
       <c r="B3" t="n">
         <v>361</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>44560</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -696,7 +684,7 @@
       <c r="B4" t="n">
         <v>953</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>44557</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -771,7 +759,7 @@
       <c r="B5" t="n">
         <v>954</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>44557</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -846,7 +834,7 @@
       <c r="B6" t="n">
         <v>752</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>44559</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -921,7 +909,7 @@
       <c r="B7" t="n">
         <v>578</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>44560</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -996,7 +984,7 @@
       <c r="B8" t="n">
         <v>605</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="1" t="n">
         <v>44560</v>
       </c>
       <c r="D8" t="inlineStr">
